--- a/output/yearly_population_iteration_6_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_6_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4798</v>
+        <v>4196</v>
       </c>
       <c r="C2" t="n">
-        <v>7358</v>
+        <v>18047</v>
       </c>
       <c r="D2" t="n">
-        <v>19971</v>
+        <v>29545</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3299</v>
+        <v>3287</v>
       </c>
       <c r="C3" t="n">
-        <v>4564</v>
+        <v>7448</v>
       </c>
       <c r="D3" t="n">
-        <v>11340</v>
+        <v>15571</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2677</v>
+        <v>2611</v>
       </c>
       <c r="C4" t="n">
-        <v>4451</v>
+        <v>4728</v>
       </c>
       <c r="D4" t="n">
-        <v>6027</v>
+        <v>6965</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1613</v>
+        <v>1629</v>
       </c>
       <c r="C5" t="n">
-        <v>3880</v>
+        <v>4628</v>
       </c>
       <c r="D5" t="n">
-        <v>2440</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>862</v>
+        <v>898</v>
       </c>
       <c r="C6" t="n">
-        <v>2808</v>
+        <v>4083</v>
       </c>
       <c r="D6" t="n">
-        <v>1126</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C7" t="n">
-        <v>1944</v>
+        <v>2855</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C8" t="n">
-        <v>1119</v>
+        <v>1463</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>418</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>480</v>
+        <v>536</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7152</v>
+        <v>5357</v>
       </c>
       <c r="C2" t="n">
-        <v>8193</v>
+        <v>19329</v>
       </c>
       <c r="D2" t="n">
-        <v>28357</v>
+        <v>29058</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3252</v>
+        <v>3017</v>
       </c>
       <c r="C3" t="n">
-        <v>5148</v>
+        <v>10575</v>
       </c>
       <c r="D3" t="n">
-        <v>11751</v>
+        <v>16338</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2554</v>
+        <v>2471</v>
       </c>
       <c r="C4" t="n">
-        <v>4371</v>
+        <v>5811</v>
       </c>
       <c r="D4" t="n">
-        <v>6653</v>
+        <v>8008</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1829</v>
+        <v>1793</v>
       </c>
       <c r="C5" t="n">
-        <v>4073</v>
+        <v>4575</v>
       </c>
       <c r="D5" t="n">
-        <v>2951</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="C6" t="n">
-        <v>3246</v>
+        <v>4235</v>
       </c>
       <c r="D6" t="n">
-        <v>1301</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C7" t="n">
-        <v>2341</v>
+        <v>3371</v>
       </c>
       <c r="D7" t="n">
-        <v>718</v>
+        <v>678</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C8" t="n">
-        <v>1482</v>
+        <v>2007</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>744</v>
+        <v>893</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
         <v>160</v>
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
         <v>127</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7924</v>
+        <v>6195</v>
       </c>
       <c r="C2" t="n">
-        <v>10644</v>
+        <v>14359</v>
       </c>
       <c r="D2" t="n">
-        <v>29438</v>
+        <v>29149</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3921</v>
+        <v>3170</v>
       </c>
       <c r="C3" t="n">
-        <v>5699</v>
+        <v>12537</v>
       </c>
       <c r="D3" t="n">
-        <v>13105</v>
+        <v>16975</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2429</v>
+        <v>2289</v>
       </c>
       <c r="C4" t="n">
-        <v>4630</v>
+        <v>7555</v>
       </c>
       <c r="D4" t="n">
-        <v>7233</v>
+        <v>8807</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1891</v>
+        <v>1825</v>
       </c>
       <c r="C5" t="n">
-        <v>4077</v>
+        <v>4922</v>
       </c>
       <c r="D5" t="n">
-        <v>3366</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1275</v>
+        <v>1229</v>
       </c>
       <c r="C6" t="n">
-        <v>3533</v>
+        <v>4288</v>
       </c>
       <c r="D6" t="n">
-        <v>1521</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="C7" t="n">
-        <v>2721</v>
+        <v>3699</v>
       </c>
       <c r="D7" t="n">
-        <v>783</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C8" t="n">
-        <v>1812</v>
+        <v>2481</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C9" t="n">
-        <v>1032</v>
+        <v>1276</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>482</v>
+        <v>531</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
         <v>239</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1612,10 +1612,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7148</v>
+        <v>5718</v>
       </c>
       <c r="C2" t="n">
-        <v>7152</v>
+        <v>10108</v>
       </c>
       <c r="D2" t="n">
-        <v>23818</v>
+        <v>24296</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4608</v>
+        <v>3894</v>
       </c>
       <c r="C3" t="n">
-        <v>8655</v>
+        <v>16750</v>
       </c>
       <c r="D3" t="n">
-        <v>14465</v>
+        <v>18108</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1747</v>
+        <v>1686</v>
       </c>
       <c r="C4" t="n">
-        <v>6536</v>
+        <v>8641</v>
       </c>
       <c r="D4" t="n">
-        <v>7085</v>
+        <v>8174</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1178</v>
+        <v>1135</v>
       </c>
       <c r="C5" t="n">
-        <v>3462</v>
+        <v>4202</v>
       </c>
       <c r="D5" t="n">
-        <v>2427</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="C6" t="n">
-        <v>2666</v>
+        <v>3625</v>
       </c>
       <c r="D6" t="n">
-        <v>767</v>
+        <v>717</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C7" t="n">
-        <v>1775</v>
+        <v>2431</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>453</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>1011</v>
+        <v>1250</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>472</v>
+        <v>520</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
         <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>49</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4175</v>
+        <v>3477</v>
       </c>
       <c r="C2" t="n">
-        <v>3638</v>
+        <v>4518</v>
       </c>
       <c r="D2" t="n">
-        <v>17838</v>
+        <v>17421</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4896</v>
+        <v>3994</v>
       </c>
       <c r="C3" t="n">
-        <v>7212</v>
+        <v>12645</v>
       </c>
       <c r="D3" t="n">
-        <v>14903</v>
+        <v>17886</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2475</v>
+        <v>2167</v>
       </c>
       <c r="C4" t="n">
-        <v>7585</v>
+        <v>12374</v>
       </c>
       <c r="D4" t="n">
-        <v>8139</v>
+        <v>9512</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1323</v>
+        <v>1263</v>
       </c>
       <c r="C5" t="n">
-        <v>4854</v>
+        <v>6020</v>
       </c>
       <c r="D5" t="n">
-        <v>2981</v>
+        <v>2983</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>764</v>
+        <v>721</v>
       </c>
       <c r="C6" t="n">
-        <v>3110</v>
+        <v>3995</v>
       </c>
       <c r="D6" t="n">
-        <v>939</v>
+        <v>869</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C7" t="n">
-        <v>2157</v>
+        <v>2936</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>1296</v>
+        <v>1597</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C9" t="n">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
         <v>165</v>
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4918</v>
+        <v>2826</v>
       </c>
       <c r="C2" t="n">
-        <v>5566</v>
+        <v>5783</v>
       </c>
       <c r="D2" t="n">
-        <v>20055</v>
+        <v>18944</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3889</v>
+        <v>3188</v>
       </c>
       <c r="C3" t="n">
-        <v>4865</v>
+        <v>8083</v>
       </c>
       <c r="D3" t="n">
-        <v>14300</v>
+        <v>16653</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3017</v>
+        <v>2508</v>
       </c>
       <c r="C4" t="n">
-        <v>7241</v>
+        <v>12241</v>
       </c>
       <c r="D4" t="n">
-        <v>9060</v>
+        <v>10509</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1613</v>
+        <v>1446</v>
       </c>
       <c r="C5" t="n">
-        <v>6063</v>
+        <v>8700</v>
       </c>
       <c r="D5" t="n">
-        <v>3732</v>
+        <v>3832</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>925</v>
+        <v>851</v>
       </c>
       <c r="C6" t="n">
-        <v>3913</v>
+        <v>4852</v>
       </c>
       <c r="D6" t="n">
-        <v>1240</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>408</v>
+        <v>377</v>
       </c>
       <c r="C7" t="n">
-        <v>2597</v>
+        <v>3360</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>1662</v>
+        <v>2123</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>828</v>
+        <v>922</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2860</v>
+        <v>1733</v>
       </c>
       <c r="C2" t="n">
-        <v>2566</v>
+        <v>2863</v>
       </c>
       <c r="D2" t="n">
-        <v>13859</v>
+        <v>13364</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3996</v>
+        <v>3005</v>
       </c>
       <c r="C3" t="n">
-        <v>4950</v>
+        <v>7158</v>
       </c>
       <c r="D3" t="n">
-        <v>14601</v>
+        <v>16526</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3350</v>
+        <v>2742</v>
       </c>
       <c r="C4" t="n">
-        <v>6987</v>
+        <v>11924</v>
       </c>
       <c r="D4" t="n">
-        <v>9722</v>
+        <v>11239</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1677</v>
+        <v>1492</v>
       </c>
       <c r="C5" t="n">
-        <v>7165</v>
+        <v>10845</v>
       </c>
       <c r="D5" t="n">
-        <v>4052</v>
+        <v>3941</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>761</v>
+        <v>670</v>
       </c>
       <c r="C6" t="n">
-        <v>4877</v>
+        <v>5646</v>
       </c>
       <c r="D6" t="n">
-        <v>1228</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>2863</v>
+        <v>3638</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n">
-        <v>1332</v>
+        <v>1486</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3924</v>
+        <v>2679</v>
       </c>
       <c r="C2" t="n">
-        <v>4417</v>
+        <v>9853</v>
       </c>
       <c r="D2" t="n">
-        <v>14593</v>
+        <v>15527</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3003</v>
+        <v>2139</v>
       </c>
       <c r="C3" t="n">
-        <v>3395</v>
+        <v>4787</v>
       </c>
       <c r="D3" t="n">
-        <v>13518</v>
+        <v>15195</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3159</v>
+        <v>2512</v>
       </c>
       <c r="C4" t="n">
-        <v>5911</v>
+        <v>9571</v>
       </c>
       <c r="D4" t="n">
-        <v>10222</v>
+        <v>11658</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2094</v>
+        <v>1749</v>
       </c>
       <c r="C5" t="n">
-        <v>7002</v>
+        <v>11179</v>
       </c>
       <c r="D5" t="n">
-        <v>4799</v>
+        <v>4802</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1017</v>
+        <v>864</v>
       </c>
       <c r="C6" t="n">
-        <v>5867</v>
+        <v>7699</v>
       </c>
       <c r="D6" t="n">
-        <v>1630</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="C7" t="n">
-        <v>3746</v>
+        <v>4455</v>
       </c>
       <c r="D7" t="n">
-        <v>656</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1927</v>
+        <v>2231</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2549</v>
+        <v>1876</v>
       </c>
       <c r="C2" t="n">
-        <v>2623</v>
+        <v>5111</v>
       </c>
       <c r="D2" t="n">
-        <v>10762</v>
+        <v>12009</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2895</v>
+        <v>2016</v>
       </c>
       <c r="C3" t="n">
-        <v>3450</v>
+        <v>6035</v>
       </c>
       <c r="D3" t="n">
-        <v>12911</v>
+        <v>14575</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2838</v>
+        <v>2204</v>
       </c>
       <c r="C4" t="n">
-        <v>4895</v>
+        <v>7856</v>
       </c>
       <c r="D4" t="n">
-        <v>10452</v>
+        <v>11822</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2309</v>
+        <v>1882</v>
       </c>
       <c r="C5" t="n">
-        <v>6716</v>
+        <v>10743</v>
       </c>
       <c r="D5" t="n">
-        <v>5369</v>
+        <v>5360</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1220</v>
+        <v>984</v>
       </c>
       <c r="C6" t="n">
-        <v>6472</v>
+        <v>8997</v>
       </c>
       <c r="D6" t="n">
-        <v>1916</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>275</v>
+        <v>214</v>
       </c>
       <c r="C7" t="n">
-        <v>4541</v>
+        <v>5458</v>
       </c>
       <c r="D7" t="n">
-        <v>733</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>2426</v>
+        <v>2756</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>805</v>
+        <v>717</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3376</v>
+        <v>2436</v>
       </c>
       <c r="C2" t="n">
-        <v>6540</v>
+        <v>5913</v>
       </c>
       <c r="D2" t="n">
-        <v>11601</v>
+        <v>14093</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2328</v>
+        <v>1661</v>
       </c>
       <c r="C3" t="n">
-        <v>2786</v>
+        <v>5094</v>
       </c>
       <c r="D3" t="n">
-        <v>11912</v>
+        <v>13378</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2484</v>
+        <v>1862</v>
       </c>
       <c r="C4" t="n">
-        <v>4121</v>
+        <v>6975</v>
       </c>
       <c r="D4" t="n">
-        <v>10388</v>
+        <v>11832</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2297</v>
+        <v>1834</v>
       </c>
       <c r="C5" t="n">
-        <v>5807</v>
+        <v>9438</v>
       </c>
       <c r="D5" t="n">
-        <v>5937</v>
+        <v>6003</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1483</v>
+        <v>1159</v>
       </c>
       <c r="C6" t="n">
-        <v>6576</v>
+        <v>9547</v>
       </c>
       <c r="D6" t="n">
-        <v>2355</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>514</v>
+        <v>388</v>
       </c>
       <c r="C7" t="n">
-        <v>5277</v>
+        <v>6669</v>
       </c>
       <c r="D7" t="n">
-        <v>876</v>
+        <v>774</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>3215</v>
+        <v>3655</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>1344</v>
+        <v>1323</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>425</v>
+        <v>355</v>
       </c>
       <c r="D10" t="n">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4097</v>
+        <v>4640</v>
       </c>
       <c r="C2" t="n">
-        <v>12067</v>
+        <v>16527</v>
       </c>
       <c r="D2" t="n">
-        <v>12346</v>
+        <v>6007</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2389</v>
+        <v>1797</v>
       </c>
       <c r="C2" t="n">
-        <v>3662</v>
+        <v>3548</v>
       </c>
       <c r="D2" t="n">
-        <v>8538</v>
+        <v>10598</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3069</v>
+        <v>2221</v>
       </c>
       <c r="C3" t="n">
-        <v>3923</v>
+        <v>5864</v>
       </c>
       <c r="D3" t="n">
-        <v>12876</v>
+        <v>14428</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3392</v>
+        <v>2630</v>
       </c>
       <c r="C4" t="n">
-        <v>6005</v>
+        <v>10166</v>
       </c>
       <c r="D4" t="n">
-        <v>10642</v>
+        <v>11948</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1455</v>
+        <v>1070</v>
       </c>
       <c r="C5" t="n">
-        <v>8937</v>
+        <v>13564</v>
       </c>
       <c r="D5" t="n">
-        <v>5485</v>
+        <v>5331</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>474</v>
+        <v>358</v>
       </c>
       <c r="C6" t="n">
-        <v>6524</v>
+        <v>8126</v>
       </c>
       <c r="D6" t="n">
-        <v>1892</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3150</v>
+        <v>3581</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>1317</v>
+        <v>1296</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>416</v>
+        <v>347</v>
       </c>
       <c r="D9" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5801</v>
+        <v>6697</v>
       </c>
       <c r="C2" t="n">
-        <v>5372</v>
+        <v>8675</v>
       </c>
       <c r="D2" t="n">
-        <v>12401</v>
+        <v>6418</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1742</v>
+        <v>1972</v>
       </c>
       <c r="C3" t="n">
-        <v>6081</v>
+        <v>8329</v>
       </c>
       <c r="D3" t="n">
-        <v>2713</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4181</v>
+        <v>4791</v>
       </c>
       <c r="C2" t="n">
-        <v>3140</v>
+        <v>8356</v>
       </c>
       <c r="D2" t="n">
-        <v>14306</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3094</v>
+        <v>3555</v>
       </c>
       <c r="C3" t="n">
-        <v>4898</v>
+        <v>7351</v>
       </c>
       <c r="D3" t="n">
-        <v>4140</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>791</v>
+        <v>891</v>
       </c>
       <c r="C4" t="n">
-        <v>3607</v>
+        <v>4923</v>
       </c>
       <c r="D4" t="n">
-        <v>1728</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4896,7 +4896,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4453</v>
+        <v>4578</v>
       </c>
       <c r="C2" t="n">
-        <v>4597</v>
+        <v>6152</v>
       </c>
       <c r="D2" t="n">
-        <v>20804</v>
+        <v>28199</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2983</v>
+        <v>3414</v>
       </c>
       <c r="C3" t="n">
-        <v>3409</v>
+        <v>6841</v>
       </c>
       <c r="D3" t="n">
-        <v>5468</v>
+        <v>4987</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1648</v>
+        <v>1856</v>
       </c>
       <c r="C4" t="n">
-        <v>4263</v>
+        <v>6172</v>
       </c>
       <c r="D4" t="n">
-        <v>2138</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>379</v>
+        <v>420</v>
       </c>
       <c r="C5" t="n">
-        <v>2069</v>
+        <v>2742</v>
       </c>
       <c r="D5" t="n">
-        <v>1246</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
         <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
         <v>371</v>
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
         <v>176</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4763</v>
+        <v>4421</v>
       </c>
       <c r="C2" t="n">
-        <v>7537</v>
+        <v>7489</v>
       </c>
       <c r="D2" t="n">
-        <v>20125</v>
+        <v>34933</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3021</v>
+        <v>3255</v>
       </c>
       <c r="C3" t="n">
-        <v>3499</v>
+        <v>5662</v>
       </c>
       <c r="D3" t="n">
-        <v>7414</v>
+        <v>8164</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1966</v>
+        <v>2223</v>
       </c>
       <c r="C4" t="n">
-        <v>3715</v>
+        <v>6396</v>
       </c>
       <c r="D4" t="n">
-        <v>2680</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>827</v>
+        <v>916</v>
       </c>
       <c r="C5" t="n">
-        <v>3143</v>
+        <v>4430</v>
       </c>
       <c r="D5" t="n">
-        <v>1350</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C6" t="n">
-        <v>1197</v>
+        <v>1491</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>928</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
         <v>188</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6290</v>
+        <v>7274</v>
       </c>
       <c r="C2" t="n">
-        <v>7073</v>
+        <v>6089</v>
       </c>
       <c r="D2" t="n">
-        <v>23022</v>
+        <v>28328</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2810</v>
+        <v>2770</v>
       </c>
       <c r="C3" t="n">
-        <v>4556</v>
+        <v>5381</v>
       </c>
       <c r="D3" t="n">
-        <v>8301</v>
+        <v>10762</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1537</v>
+        <v>1691</v>
       </c>
       <c r="C4" t="n">
-        <v>2945</v>
+        <v>4858</v>
       </c>
       <c r="D4" t="n">
-        <v>3019</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>729</v>
+        <v>799</v>
       </c>
       <c r="C5" t="n">
-        <v>2484</v>
+        <v>3957</v>
       </c>
       <c r="D5" t="n">
-        <v>1236</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="C6" t="n">
-        <v>1467</v>
+        <v>1961</v>
       </c>
       <c r="D6" t="n">
-        <v>776</v>
+        <v>738</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>486</v>
+        <v>564</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5689</v>
+        <v>4911</v>
       </c>
       <c r="C2" t="n">
-        <v>5475</v>
+        <v>5841</v>
       </c>
       <c r="D2" t="n">
-        <v>20380</v>
+        <v>26956</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3792</v>
+        <v>4124</v>
       </c>
       <c r="C3" t="n">
-        <v>5195</v>
+        <v>5034</v>
       </c>
       <c r="D3" t="n">
-        <v>10267</v>
+        <v>12921</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1910</v>
+        <v>1923</v>
       </c>
       <c r="C4" t="n">
-        <v>3873</v>
+        <v>5016</v>
       </c>
       <c r="D4" t="n">
-        <v>4042</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1004</v>
+        <v>1104</v>
       </c>
       <c r="C5" t="n">
-        <v>2706</v>
+        <v>4393</v>
       </c>
       <c r="D5" t="n">
-        <v>1557</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="C6" t="n">
-        <v>2034</v>
+        <v>3048</v>
       </c>
       <c r="D6" t="n">
-        <v>845</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>1043</v>
+        <v>1330</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>367</v>
+        <v>403</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>81</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4103</v>
+        <v>4322</v>
       </c>
       <c r="C2" t="n">
-        <v>5835</v>
+        <v>12653</v>
       </c>
       <c r="D2" t="n">
-        <v>17593</v>
+        <v>30813</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3890</v>
+        <v>3708</v>
       </c>
       <c r="C3" t="n">
-        <v>4622</v>
+        <v>4741</v>
       </c>
       <c r="D3" t="n">
-        <v>11145</v>
+        <v>14144</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2461</v>
+        <v>2536</v>
       </c>
       <c r="C4" t="n">
-        <v>4553</v>
+        <v>4921</v>
       </c>
       <c r="D4" t="n">
-        <v>5075</v>
+        <v>5674</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1272</v>
+        <v>1324</v>
       </c>
       <c r="C5" t="n">
-        <v>3299</v>
+        <v>4630</v>
       </c>
       <c r="D5" t="n">
-        <v>1986</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>667</v>
+        <v>705</v>
       </c>
       <c r="C6" t="n">
-        <v>2371</v>
+        <v>3668</v>
       </c>
       <c r="D6" t="n">
-        <v>963</v>
+        <v>888</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>1567</v>
+        <v>2204</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>707</v>
+        <v>857</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="D9" t="n">
         <v>291</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>122</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_6_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_6_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4196</v>
+        <v>6096</v>
       </c>
       <c r="C2" t="n">
-        <v>18047</v>
+        <v>13998</v>
       </c>
       <c r="D2" t="n">
-        <v>29545</v>
+        <v>24706</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3287</v>
+        <v>3965</v>
       </c>
       <c r="C3" t="n">
-        <v>7448</v>
+        <v>4958</v>
       </c>
       <c r="D3" t="n">
-        <v>15571</v>
+        <v>14208</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2611</v>
+        <v>3194</v>
       </c>
       <c r="C4" t="n">
-        <v>4728</v>
+        <v>4052</v>
       </c>
       <c r="D4" t="n">
-        <v>6965</v>
+        <v>6754</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1629</v>
+        <v>2075</v>
       </c>
       <c r="C5" t="n">
-        <v>4628</v>
+        <v>3413</v>
       </c>
       <c r="D5" t="n">
-        <v>2410</v>
+        <v>2621</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>898</v>
+        <v>1194</v>
       </c>
       <c r="C6" t="n">
-        <v>4083</v>
+        <v>2391</v>
       </c>
       <c r="D6" t="n">
-        <v>1035</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>414</v>
+        <v>589</v>
       </c>
       <c r="C7" t="n">
-        <v>2855</v>
+        <v>1406</v>
       </c>
       <c r="D7" t="n">
-        <v>624</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>154</v>
+        <v>228</v>
       </c>
       <c r="C8" t="n">
-        <v>1463</v>
+        <v>678</v>
       </c>
       <c r="D8" t="n">
-        <v>418</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
-        <v>536</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
         <v>159</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5357</v>
+        <v>9359</v>
       </c>
       <c r="C2" t="n">
-        <v>19329</v>
+        <v>8472</v>
       </c>
       <c r="D2" t="n">
-        <v>29058</v>
+        <v>29436</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3017</v>
+        <v>4022</v>
       </c>
       <c r="C3" t="n">
-        <v>10575</v>
+        <v>8155</v>
       </c>
       <c r="D3" t="n">
-        <v>16338</v>
+        <v>14680</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2471</v>
+        <v>3058</v>
       </c>
       <c r="C4" t="n">
-        <v>5811</v>
+        <v>4372</v>
       </c>
       <c r="D4" t="n">
-        <v>8008</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1793</v>
+        <v>2266</v>
       </c>
       <c r="C5" t="n">
-        <v>4575</v>
+        <v>3648</v>
       </c>
       <c r="D5" t="n">
-        <v>3036</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1087</v>
+        <v>1439</v>
       </c>
       <c r="C6" t="n">
-        <v>4235</v>
+        <v>2814</v>
       </c>
       <c r="D6" t="n">
-        <v>1209</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>551</v>
+        <v>773</v>
       </c>
       <c r="C7" t="n">
-        <v>3371</v>
+        <v>1859</v>
       </c>
       <c r="D7" t="n">
-        <v>678</v>
+        <v>726</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>225</v>
+        <v>336</v>
       </c>
       <c r="C8" t="n">
-        <v>2007</v>
+        <v>992</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="C9" t="n">
-        <v>893</v>
+        <v>473</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>348</v>
+        <v>253</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6195</v>
+        <v>9809</v>
       </c>
       <c r="C2" t="n">
-        <v>14359</v>
+        <v>7260</v>
       </c>
       <c r="D2" t="n">
-        <v>29149</v>
+        <v>30752</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3170</v>
+        <v>5010</v>
       </c>
       <c r="C3" t="n">
-        <v>12537</v>
+        <v>7334</v>
       </c>
       <c r="D3" t="n">
-        <v>16975</v>
+        <v>15605</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2289</v>
+        <v>2951</v>
       </c>
       <c r="C4" t="n">
-        <v>7555</v>
+        <v>5945</v>
       </c>
       <c r="D4" t="n">
-        <v>8807</v>
+        <v>8464</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1825</v>
+        <v>2309</v>
       </c>
       <c r="C5" t="n">
-        <v>4922</v>
+        <v>3891</v>
       </c>
       <c r="D5" t="n">
-        <v>3582</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1229</v>
+        <v>1638</v>
       </c>
       <c r="C6" t="n">
-        <v>4288</v>
+        <v>3112</v>
       </c>
       <c r="D6" t="n">
-        <v>1438</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>672</v>
+        <v>936</v>
       </c>
       <c r="C7" t="n">
-        <v>3699</v>
+        <v>2260</v>
       </c>
       <c r="D7" t="n">
-        <v>732</v>
+        <v>811</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>303</v>
+        <v>450</v>
       </c>
       <c r="C8" t="n">
-        <v>2481</v>
+        <v>1330</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="C9" t="n">
-        <v>1276</v>
+        <v>671</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C10" t="n">
-        <v>531</v>
+        <v>336</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
         <v>163</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5718</v>
+        <v>8883</v>
       </c>
       <c r="C2" t="n">
-        <v>10108</v>
+        <v>4878</v>
       </c>
       <c r="D2" t="n">
-        <v>24296</v>
+        <v>24954</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3894</v>
+        <v>5758</v>
       </c>
       <c r="C3" t="n">
-        <v>16750</v>
+        <v>10309</v>
       </c>
       <c r="D3" t="n">
-        <v>18108</v>
+        <v>17146</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1686</v>
+        <v>2133</v>
       </c>
       <c r="C4" t="n">
-        <v>8641</v>
+        <v>7102</v>
       </c>
       <c r="D4" t="n">
-        <v>8174</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1135</v>
+        <v>1513</v>
       </c>
       <c r="C5" t="n">
-        <v>4202</v>
+        <v>3049</v>
       </c>
       <c r="D5" t="n">
-        <v>2337</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>620</v>
+        <v>864</v>
       </c>
       <c r="C6" t="n">
-        <v>3625</v>
+        <v>2214</v>
       </c>
       <c r="D6" t="n">
-        <v>717</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>415</v>
       </c>
       <c r="C7" t="n">
-        <v>2431</v>
+        <v>1303</v>
       </c>
       <c r="D7" t="n">
-        <v>453</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="C8" t="n">
-        <v>1250</v>
+        <v>657</v>
       </c>
       <c r="D8" t="n">
-        <v>316</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>520</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
         <v>159</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3477</v>
+        <v>5304</v>
       </c>
       <c r="C2" t="n">
-        <v>4518</v>
+        <v>2638</v>
       </c>
       <c r="D2" t="n">
-        <v>17421</v>
+        <v>17645</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3994</v>
+        <v>6102</v>
       </c>
       <c r="C3" t="n">
-        <v>12645</v>
+        <v>7016</v>
       </c>
       <c r="D3" t="n">
-        <v>17886</v>
+        <v>17220</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2167</v>
+        <v>3061</v>
       </c>
       <c r="C4" t="n">
-        <v>12374</v>
+        <v>8766</v>
       </c>
       <c r="D4" t="n">
-        <v>9512</v>
+        <v>9482</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1263</v>
+        <v>1674</v>
       </c>
       <c r="C5" t="n">
-        <v>6020</v>
+        <v>4843</v>
       </c>
       <c r="D5" t="n">
-        <v>2983</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>721</v>
+        <v>1032</v>
       </c>
       <c r="C6" t="n">
-        <v>3995</v>
+        <v>2623</v>
       </c>
       <c r="D6" t="n">
-        <v>869</v>
+        <v>983</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>260</v>
+        <v>395</v>
       </c>
       <c r="C7" t="n">
-        <v>2936</v>
+        <v>1676</v>
       </c>
       <c r="D7" t="n">
-        <v>494</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="C8" t="n">
-        <v>1597</v>
+        <v>867</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>539</v>
+        <v>382</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2826</v>
+        <v>5736</v>
       </c>
       <c r="C2" t="n">
-        <v>5783</v>
+        <v>4146</v>
       </c>
       <c r="D2" t="n">
-        <v>18944</v>
+        <v>15924</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3188</v>
+        <v>4830</v>
       </c>
       <c r="C3" t="n">
-        <v>8083</v>
+        <v>4351</v>
       </c>
       <c r="D3" t="n">
-        <v>16653</v>
+        <v>16096</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2508</v>
+        <v>3800</v>
       </c>
       <c r="C4" t="n">
-        <v>12241</v>
+        <v>7710</v>
       </c>
       <c r="D4" t="n">
-        <v>10509</v>
+        <v>10530</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1446</v>
+        <v>2017</v>
       </c>
       <c r="C5" t="n">
-        <v>8700</v>
+        <v>6625</v>
       </c>
       <c r="D5" t="n">
-        <v>3832</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>851</v>
+        <v>1211</v>
       </c>
       <c r="C6" t="n">
-        <v>4852</v>
+        <v>3645</v>
       </c>
       <c r="D6" t="n">
-        <v>1141</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>570</v>
       </c>
       <c r="C7" t="n">
-        <v>3360</v>
+        <v>2109</v>
       </c>
       <c r="D7" t="n">
-        <v>536</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>204</v>
       </c>
       <c r="C8" t="n">
-        <v>2123</v>
+        <v>1208</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>922</v>
+        <v>570</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>337</v>
+        <v>284</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1733</v>
+        <v>3384</v>
       </c>
       <c r="C2" t="n">
-        <v>2863</v>
+        <v>1935</v>
       </c>
       <c r="D2" t="n">
-        <v>13364</v>
+        <v>10991</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3005</v>
+        <v>4874</v>
       </c>
       <c r="C3" t="n">
-        <v>7158</v>
+        <v>4099</v>
       </c>
       <c r="D3" t="n">
-        <v>16526</v>
+        <v>15690</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2742</v>
+        <v>4208</v>
       </c>
       <c r="C4" t="n">
-        <v>11924</v>
+        <v>7202</v>
       </c>
       <c r="D4" t="n">
-        <v>11239</v>
+        <v>11249</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1492</v>
+        <v>2125</v>
       </c>
       <c r="C5" t="n">
-        <v>10845</v>
+        <v>7760</v>
       </c>
       <c r="D5" t="n">
-        <v>3941</v>
+        <v>4564</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>670</v>
+        <v>1030</v>
       </c>
       <c r="C6" t="n">
-        <v>5646</v>
+        <v>4515</v>
       </c>
       <c r="D6" t="n">
-        <v>1120</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="C7" t="n">
-        <v>3638</v>
+        <v>2231</v>
       </c>
       <c r="D7" t="n">
-        <v>539</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>1486</v>
+        <v>937</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>330</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2679</v>
+        <v>4350</v>
       </c>
       <c r="C2" t="n">
-        <v>9853</v>
+        <v>2761</v>
       </c>
       <c r="D2" t="n">
-        <v>15527</v>
+        <v>11109</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2139</v>
+        <v>3628</v>
       </c>
       <c r="C3" t="n">
-        <v>4787</v>
+        <v>2717</v>
       </c>
       <c r="D3" t="n">
-        <v>15195</v>
+        <v>13996</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2512</v>
+        <v>3919</v>
       </c>
       <c r="C4" t="n">
-        <v>9571</v>
+        <v>5602</v>
       </c>
       <c r="D4" t="n">
-        <v>11658</v>
+        <v>11631</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1749</v>
+        <v>2642</v>
       </c>
       <c r="C5" t="n">
-        <v>11179</v>
+        <v>7415</v>
       </c>
       <c r="D5" t="n">
-        <v>4802</v>
+        <v>5452</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>864</v>
+        <v>1333</v>
       </c>
       <c r="C6" t="n">
-        <v>7699</v>
+        <v>5918</v>
       </c>
       <c r="D6" t="n">
-        <v>1457</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>243</v>
+        <v>401</v>
       </c>
       <c r="C7" t="n">
-        <v>4455</v>
+        <v>3213</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>2231</v>
+        <v>1436</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>679</v>
+        <v>505</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1876</v>
+        <v>3261</v>
       </c>
       <c r="C2" t="n">
-        <v>5111</v>
+        <v>2212</v>
       </c>
       <c r="D2" t="n">
-        <v>12009</v>
+        <v>8403</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2016</v>
+        <v>3385</v>
       </c>
       <c r="C3" t="n">
-        <v>6035</v>
+        <v>2476</v>
       </c>
       <c r="D3" t="n">
-        <v>14575</v>
+        <v>12888</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2204</v>
+        <v>3495</v>
       </c>
       <c r="C4" t="n">
-        <v>7856</v>
+        <v>4428</v>
       </c>
       <c r="D4" t="n">
-        <v>11822</v>
+        <v>11706</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1882</v>
+        <v>2900</v>
       </c>
       <c r="C5" t="n">
-        <v>10743</v>
+        <v>6866</v>
       </c>
       <c r="D5" t="n">
-        <v>5360</v>
+        <v>6102</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>984</v>
+        <v>1587</v>
       </c>
       <c r="C6" t="n">
-        <v>8997</v>
+        <v>6640</v>
       </c>
       <c r="D6" t="n">
-        <v>1739</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>214</v>
+        <v>377</v>
       </c>
       <c r="C7" t="n">
-        <v>5458</v>
+        <v>4121</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>761</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>2756</v>
+        <v>1877</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>717</v>
+        <v>604</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2436</v>
+        <v>6011</v>
       </c>
       <c r="C2" t="n">
-        <v>5913</v>
+        <v>5718</v>
       </c>
       <c r="D2" t="n">
-        <v>14093</v>
+        <v>16883</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1661</v>
+        <v>2808</v>
       </c>
       <c r="C3" t="n">
-        <v>5094</v>
+        <v>2097</v>
       </c>
       <c r="D3" t="n">
-        <v>13378</v>
+        <v>11592</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1862</v>
+        <v>3002</v>
       </c>
       <c r="C4" t="n">
-        <v>6975</v>
+        <v>3473</v>
       </c>
       <c r="D4" t="n">
-        <v>11832</v>
+        <v>11407</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1834</v>
+        <v>2864</v>
       </c>
       <c r="C5" t="n">
-        <v>9438</v>
+        <v>5693</v>
       </c>
       <c r="D5" t="n">
-        <v>6003</v>
+        <v>6723</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1159</v>
+        <v>1898</v>
       </c>
       <c r="C6" t="n">
-        <v>9547</v>
+        <v>6737</v>
       </c>
       <c r="D6" t="n">
-        <v>2134</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>388</v>
+        <v>683</v>
       </c>
       <c r="C7" t="n">
-        <v>6669</v>
+        <v>5082</v>
       </c>
       <c r="D7" t="n">
-        <v>774</v>
+        <v>923</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="C8" t="n">
-        <v>3655</v>
+        <v>2708</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>1323</v>
+        <v>1027</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4640</v>
+        <v>7860</v>
       </c>
       <c r="C2" t="n">
-        <v>16527</v>
+        <v>4818</v>
       </c>
       <c r="D2" t="n">
-        <v>6007</v>
+        <v>7890</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1797</v>
+        <v>4252</v>
       </c>
       <c r="C2" t="n">
-        <v>3548</v>
+        <v>3202</v>
       </c>
       <c r="D2" t="n">
-        <v>10598</v>
+        <v>12425</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2221</v>
+        <v>3890</v>
       </c>
       <c r="C3" t="n">
-        <v>5864</v>
+        <v>3143</v>
       </c>
       <c r="D3" t="n">
-        <v>14428</v>
+        <v>12975</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2630</v>
+        <v>4177</v>
       </c>
       <c r="C4" t="n">
-        <v>10166</v>
+        <v>5269</v>
       </c>
       <c r="D4" t="n">
-        <v>11948</v>
+        <v>11733</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1070</v>
+        <v>1859</v>
       </c>
       <c r="C5" t="n">
-        <v>13564</v>
+        <v>8986</v>
       </c>
       <c r="D5" t="n">
-        <v>5331</v>
+        <v>6184</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>358</v>
+        <v>631</v>
       </c>
       <c r="C6" t="n">
-        <v>8126</v>
+        <v>6366</v>
       </c>
       <c r="D6" t="n">
-        <v>1692</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="C7" t="n">
-        <v>3581</v>
+        <v>2653</v>
       </c>
       <c r="D7" t="n">
-        <v>490</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1296</v>
+        <v>1006</v>
       </c>
       <c r="D8" t="n">
-        <v>283</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6697</v>
+        <v>7349</v>
       </c>
       <c r="C2" t="n">
-        <v>8675</v>
+        <v>4368</v>
       </c>
       <c r="D2" t="n">
-        <v>6418</v>
+        <v>21225</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1972</v>
+        <v>3338</v>
       </c>
       <c r="C3" t="n">
-        <v>8329</v>
+        <v>2428</v>
       </c>
       <c r="D3" t="n">
-        <v>1648</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4791</v>
+        <v>5463</v>
       </c>
       <c r="C2" t="n">
-        <v>8356</v>
+        <v>5200</v>
       </c>
       <c r="D2" t="n">
-        <v>20000</v>
+        <v>16266</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3555</v>
+        <v>4391</v>
       </c>
       <c r="C3" t="n">
-        <v>7351</v>
+        <v>3040</v>
       </c>
       <c r="D3" t="n">
-        <v>2328</v>
+        <v>5055</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>891</v>
+        <v>1484</v>
       </c>
       <c r="C4" t="n">
-        <v>4923</v>
+        <v>1466</v>
       </c>
       <c r="D4" t="n">
-        <v>1513</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4578</v>
+        <v>5142</v>
       </c>
       <c r="C2" t="n">
-        <v>6152</v>
+        <v>5602</v>
       </c>
       <c r="D2" t="n">
-        <v>28199</v>
+        <v>19007</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3414</v>
+        <v>4049</v>
       </c>
       <c r="C3" t="n">
-        <v>6841</v>
+        <v>3650</v>
       </c>
       <c r="D3" t="n">
-        <v>4987</v>
+        <v>6484</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1856</v>
+        <v>2490</v>
       </c>
       <c r="C4" t="n">
-        <v>6172</v>
+        <v>2327</v>
       </c>
       <c r="D4" t="n">
-        <v>1623</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>420</v>
+        <v>668</v>
       </c>
       <c r="C5" t="n">
-        <v>2742</v>
+        <v>894</v>
       </c>
       <c r="D5" t="n">
-        <v>1219</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4421</v>
+        <v>5864</v>
       </c>
       <c r="C2" t="n">
-        <v>7489</v>
+        <v>5901</v>
       </c>
       <c r="D2" t="n">
-        <v>34933</v>
+        <v>24389</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3255</v>
+        <v>3761</v>
       </c>
       <c r="C3" t="n">
-        <v>5662</v>
+        <v>4051</v>
       </c>
       <c r="D3" t="n">
-        <v>8164</v>
+        <v>7931</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2223</v>
+        <v>2766</v>
       </c>
       <c r="C4" t="n">
-        <v>6396</v>
+        <v>2967</v>
       </c>
       <c r="D4" t="n">
-        <v>2187</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>916</v>
+        <v>1321</v>
       </c>
       <c r="C5" t="n">
-        <v>4430</v>
+        <v>1632</v>
       </c>
       <c r="D5" t="n">
-        <v>1251</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="C6" t="n">
-        <v>1491</v>
+        <v>600</v>
       </c>
       <c r="D6" t="n">
-        <v>928</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7274</v>
+        <v>8032</v>
       </c>
       <c r="C2" t="n">
-        <v>6089</v>
+        <v>5588</v>
       </c>
       <c r="D2" t="n">
-        <v>28328</v>
+        <v>23442</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2770</v>
+        <v>3496</v>
       </c>
       <c r="C3" t="n">
-        <v>5381</v>
+        <v>4105</v>
       </c>
       <c r="D3" t="n">
-        <v>10762</v>
+        <v>9289</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1691</v>
+        <v>2040</v>
       </c>
       <c r="C4" t="n">
-        <v>4858</v>
+        <v>2932</v>
       </c>
       <c r="D4" t="n">
-        <v>2731</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>799</v>
+        <v>1069</v>
       </c>
       <c r="C5" t="n">
-        <v>3957</v>
+        <v>1709</v>
       </c>
       <c r="D5" t="n">
-        <v>1113</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>269</v>
+        <v>398</v>
       </c>
       <c r="C6" t="n">
-        <v>1961</v>
+        <v>750</v>
       </c>
       <c r="D6" t="n">
-        <v>738</v>
+        <v>767</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>564</v>
+        <v>304</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4911</v>
+        <v>5829</v>
       </c>
       <c r="C2" t="n">
-        <v>5841</v>
+        <v>5589</v>
       </c>
       <c r="D2" t="n">
-        <v>26956</v>
+        <v>29628</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4124</v>
+        <v>4839</v>
       </c>
       <c r="C3" t="n">
-        <v>5034</v>
+        <v>4279</v>
       </c>
       <c r="D3" t="n">
-        <v>12921</v>
+        <v>11081</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1923</v>
+        <v>2442</v>
       </c>
       <c r="C4" t="n">
-        <v>5016</v>
+        <v>3591</v>
       </c>
       <c r="D4" t="n">
-        <v>4267</v>
+        <v>4405</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1104</v>
+        <v>1397</v>
       </c>
       <c r="C5" t="n">
-        <v>4393</v>
+        <v>2384</v>
       </c>
       <c r="D5" t="n">
-        <v>1379</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>488</v>
+        <v>681</v>
       </c>
       <c r="C6" t="n">
-        <v>3048</v>
+        <v>1302</v>
       </c>
       <c r="D6" t="n">
-        <v>799</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>232</v>
       </c>
       <c r="C7" t="n">
-        <v>1330</v>
+        <v>561</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>403</v>
+        <v>267</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>197</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4322</v>
+        <v>5170</v>
       </c>
       <c r="C2" t="n">
-        <v>12653</v>
+        <v>6990</v>
       </c>
       <c r="D2" t="n">
-        <v>30813</v>
+        <v>25691</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3708</v>
+        <v>4393</v>
       </c>
       <c r="C3" t="n">
-        <v>4741</v>
+        <v>4325</v>
       </c>
       <c r="D3" t="n">
-        <v>14144</v>
+        <v>13250</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2536</v>
+        <v>3143</v>
       </c>
       <c r="C4" t="n">
-        <v>4921</v>
+        <v>3912</v>
       </c>
       <c r="D4" t="n">
-        <v>5674</v>
+        <v>5510</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1324</v>
+        <v>1682</v>
       </c>
       <c r="C5" t="n">
-        <v>4630</v>
+        <v>3006</v>
       </c>
       <c r="D5" t="n">
-        <v>1863</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>705</v>
+        <v>952</v>
       </c>
       <c r="C6" t="n">
-        <v>3668</v>
+        <v>1855</v>
       </c>
       <c r="D6" t="n">
-        <v>888</v>
+        <v>981</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>280</v>
+        <v>403</v>
       </c>
       <c r="C7" t="n">
-        <v>2204</v>
+        <v>960</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>857</v>
+        <v>419</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>298</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
         <v>157</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_6_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_6_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6096</v>
+        <v>969</v>
       </c>
       <c r="C2" t="n">
-        <v>13998</v>
+        <v>4685</v>
       </c>
       <c r="D2" t="n">
-        <v>24706</v>
+        <v>10642</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3965</v>
+        <v>2041</v>
       </c>
       <c r="C3" t="n">
-        <v>4958</v>
+        <v>9402</v>
       </c>
       <c r="D3" t="n">
-        <v>14208</v>
+        <v>10827</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3194</v>
+        <v>1553</v>
       </c>
       <c r="C4" t="n">
-        <v>4052</v>
+        <v>9756</v>
       </c>
       <c r="D4" t="n">
-        <v>6754</v>
+        <v>4770</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2075</v>
+        <v>724</v>
       </c>
       <c r="C5" t="n">
-        <v>3413</v>
+        <v>5743</v>
       </c>
       <c r="D5" t="n">
-        <v>2621</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1194</v>
+        <v>298</v>
       </c>
       <c r="C6" t="n">
-        <v>2391</v>
+        <v>2427</v>
       </c>
       <c r="D6" t="n">
-        <v>1164</v>
+        <v>727</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>589</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
-        <v>1406</v>
+        <v>837</v>
       </c>
       <c r="D7" t="n">
-        <v>653</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>228</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>678</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9359</v>
+        <v>1131</v>
       </c>
       <c r="C2" t="n">
-        <v>8472</v>
+        <v>7891</v>
       </c>
       <c r="D2" t="n">
-        <v>29436</v>
+        <v>8410</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4022</v>
+        <v>1303</v>
       </c>
       <c r="C3" t="n">
-        <v>8155</v>
+        <v>6107</v>
       </c>
       <c r="D3" t="n">
-        <v>14680</v>
+        <v>10036</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3058</v>
+        <v>1554</v>
       </c>
       <c r="C4" t="n">
-        <v>4372</v>
+        <v>9362</v>
       </c>
       <c r="D4" t="n">
-        <v>7700</v>
+        <v>5729</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2266</v>
+        <v>977</v>
       </c>
       <c r="C5" t="n">
-        <v>3648</v>
+        <v>7759</v>
       </c>
       <c r="D5" t="n">
-        <v>3215</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1439</v>
+        <v>437</v>
       </c>
       <c r="C6" t="n">
-        <v>2814</v>
+        <v>4048</v>
       </c>
       <c r="D6" t="n">
-        <v>1360</v>
+        <v>869</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>773</v>
+        <v>163</v>
       </c>
       <c r="C7" t="n">
-        <v>1859</v>
+        <v>1592</v>
       </c>
       <c r="D7" t="n">
-        <v>726</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>336</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>992</v>
+        <v>572</v>
       </c>
       <c r="D8" t="n">
-        <v>463</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>473</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9809</v>
+        <v>612</v>
       </c>
       <c r="C2" t="n">
-        <v>7260</v>
+        <v>3388</v>
       </c>
       <c r="D2" t="n">
-        <v>30752</v>
+        <v>5745</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5010</v>
+        <v>1208</v>
       </c>
       <c r="C3" t="n">
-        <v>7334</v>
+        <v>6543</v>
       </c>
       <c r="D3" t="n">
-        <v>15605</v>
+        <v>9583</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2951</v>
+        <v>1668</v>
       </c>
       <c r="C4" t="n">
-        <v>5945</v>
+        <v>8847</v>
       </c>
       <c r="D4" t="n">
-        <v>8464</v>
+        <v>6284</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2309</v>
+        <v>968</v>
       </c>
       <c r="C5" t="n">
-        <v>3891</v>
+        <v>9170</v>
       </c>
       <c r="D5" t="n">
-        <v>3806</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1638</v>
+        <v>344</v>
       </c>
       <c r="C6" t="n">
-        <v>3112</v>
+        <v>5109</v>
       </c>
       <c r="D6" t="n">
-        <v>1595</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>936</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>2260</v>
+        <v>1487</v>
       </c>
       <c r="D7" t="n">
-        <v>811</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>450</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1330</v>
+        <v>506</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>179</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>671</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>340</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>336</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8883</v>
+        <v>401</v>
       </c>
       <c r="C2" t="n">
-        <v>4878</v>
+        <v>10825</v>
       </c>
       <c r="D2" t="n">
-        <v>24954</v>
+        <v>11833</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5758</v>
+        <v>806</v>
       </c>
       <c r="C3" t="n">
-        <v>10309</v>
+        <v>4353</v>
       </c>
       <c r="D3" t="n">
-        <v>17146</v>
+        <v>8371</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2133</v>
+        <v>1309</v>
       </c>
       <c r="C4" t="n">
-        <v>7102</v>
+        <v>7553</v>
       </c>
       <c r="D4" t="n">
-        <v>8200</v>
+        <v>6663</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1513</v>
+        <v>1135</v>
       </c>
       <c r="C5" t="n">
-        <v>3049</v>
+        <v>8909</v>
       </c>
       <c r="D5" t="n">
-        <v>2622</v>
+        <v>2992</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>864</v>
+        <v>535</v>
       </c>
       <c r="C6" t="n">
-        <v>2214</v>
+        <v>7029</v>
       </c>
       <c r="D6" t="n">
-        <v>794</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>415</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>1303</v>
+        <v>3077</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>657</v>
+        <v>900</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
+        <v>81</v>
+      </c>
+      <c r="D13" t="n">
         <v>92</v>
-      </c>
-      <c r="D13" t="n">
-        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>69</v>
+      </c>
+      <c r="D14" t="n">
         <v>68</v>
-      </c>
-      <c r="D14" t="n">
-        <v>82</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5304</v>
+        <v>332</v>
       </c>
       <c r="C2" t="n">
-        <v>2638</v>
+        <v>5524</v>
       </c>
       <c r="D2" t="n">
-        <v>17645</v>
+        <v>9092</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6102</v>
+        <v>578</v>
       </c>
       <c r="C3" t="n">
-        <v>7016</v>
+        <v>6499</v>
       </c>
       <c r="D3" t="n">
-        <v>17220</v>
+        <v>8345</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3061</v>
+        <v>1058</v>
       </c>
       <c r="C4" t="n">
-        <v>8766</v>
+        <v>6127</v>
       </c>
       <c r="D4" t="n">
-        <v>9482</v>
+        <v>6770</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1674</v>
+        <v>1170</v>
       </c>
       <c r="C5" t="n">
-        <v>4843</v>
+        <v>8519</v>
       </c>
       <c r="D5" t="n">
-        <v>3288</v>
+        <v>3416</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1032</v>
+        <v>654</v>
       </c>
       <c r="C6" t="n">
-        <v>2623</v>
+        <v>8038</v>
       </c>
       <c r="D6" t="n">
-        <v>983</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>395</v>
+        <v>154</v>
       </c>
       <c r="C7" t="n">
-        <v>1676</v>
+        <v>4371</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>867</v>
+        <v>1391</v>
       </c>
       <c r="D8" t="n">
-        <v>347</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>382</v>
+        <v>433</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
         <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5736</v>
+        <v>1031</v>
       </c>
       <c r="C2" t="n">
-        <v>4146</v>
+        <v>9544</v>
       </c>
       <c r="D2" t="n">
-        <v>15924</v>
+        <v>11807</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4830</v>
+        <v>406</v>
       </c>
       <c r="C3" t="n">
-        <v>4351</v>
+        <v>5365</v>
       </c>
       <c r="D3" t="n">
-        <v>16096</v>
+        <v>7893</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3800</v>
+        <v>759</v>
       </c>
       <c r="C4" t="n">
-        <v>7710</v>
+        <v>6170</v>
       </c>
       <c r="D4" t="n">
-        <v>10530</v>
+        <v>6806</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2017</v>
+        <v>1047</v>
       </c>
       <c r="C5" t="n">
-        <v>6625</v>
+        <v>7285</v>
       </c>
       <c r="D5" t="n">
-        <v>4198</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1211</v>
+        <v>784</v>
       </c>
       <c r="C6" t="n">
-        <v>3645</v>
+        <v>8245</v>
       </c>
       <c r="D6" t="n">
-        <v>1323</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>570</v>
+        <v>289</v>
       </c>
       <c r="C7" t="n">
-        <v>2109</v>
+        <v>5842</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>1208</v>
+        <v>2543</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>570</v>
+        <v>775</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3384</v>
+        <v>709</v>
       </c>
       <c r="C2" t="n">
-        <v>1935</v>
+        <v>5191</v>
       </c>
       <c r="D2" t="n">
-        <v>10991</v>
+        <v>8595</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4874</v>
+        <v>687</v>
       </c>
       <c r="C3" t="n">
-        <v>4099</v>
+        <v>6872</v>
       </c>
       <c r="D3" t="n">
-        <v>15690</v>
+        <v>8819</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4208</v>
+        <v>1339</v>
       </c>
       <c r="C4" t="n">
-        <v>7202</v>
+        <v>8672</v>
       </c>
       <c r="D4" t="n">
-        <v>11249</v>
+        <v>7016</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2125</v>
+        <v>772</v>
       </c>
       <c r="C5" t="n">
-        <v>7760</v>
+        <v>11187</v>
       </c>
       <c r="D5" t="n">
-        <v>4564</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1030</v>
+        <v>267</v>
       </c>
       <c r="C6" t="n">
-        <v>4515</v>
+        <v>7583</v>
       </c>
       <c r="D6" t="n">
-        <v>1304</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>188</v>
+        <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>2231</v>
+        <v>2492</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>937</v>
+        <v>759</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4350</v>
+        <v>388</v>
       </c>
       <c r="C2" t="n">
-        <v>2761</v>
+        <v>3064</v>
       </c>
       <c r="D2" t="n">
-        <v>11109</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3628</v>
+        <v>589</v>
       </c>
       <c r="C3" t="n">
-        <v>2717</v>
+        <v>5371</v>
       </c>
       <c r="D3" t="n">
-        <v>13996</v>
+        <v>8169</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3919</v>
+        <v>881</v>
       </c>
       <c r="C4" t="n">
-        <v>5602</v>
+        <v>7378</v>
       </c>
       <c r="D4" t="n">
-        <v>11631</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2642</v>
+        <v>714</v>
       </c>
       <c r="C5" t="n">
-        <v>7415</v>
+        <v>8815</v>
       </c>
       <c r="D5" t="n">
-        <v>5452</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1333</v>
+        <v>262</v>
       </c>
       <c r="C6" t="n">
-        <v>5918</v>
+        <v>7506</v>
       </c>
       <c r="D6" t="n">
-        <v>1769</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>401</v>
+        <v>57</v>
       </c>
       <c r="C7" t="n">
-        <v>3213</v>
+        <v>3270</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1436</v>
+        <v>891</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>505</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>123</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3261</v>
+        <v>280</v>
       </c>
       <c r="C2" t="n">
-        <v>2212</v>
+        <v>11458</v>
       </c>
       <c r="D2" t="n">
-        <v>8403</v>
+        <v>6878</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3385</v>
+        <v>416</v>
       </c>
       <c r="C3" t="n">
-        <v>2476</v>
+        <v>3665</v>
       </c>
       <c r="D3" t="n">
-        <v>12888</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3495</v>
+        <v>651</v>
       </c>
       <c r="C4" t="n">
-        <v>4428</v>
+        <v>6145</v>
       </c>
       <c r="D4" t="n">
-        <v>11706</v>
+        <v>6842</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2900</v>
+        <v>719</v>
       </c>
       <c r="C5" t="n">
-        <v>6866</v>
+        <v>7886</v>
       </c>
       <c r="D5" t="n">
-        <v>6102</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1587</v>
+        <v>420</v>
       </c>
       <c r="C6" t="n">
-        <v>6640</v>
+        <v>8151</v>
       </c>
       <c r="D6" t="n">
-        <v>2100</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>4121</v>
+        <v>5334</v>
       </c>
       <c r="D7" t="n">
-        <v>761</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1877</v>
+        <v>1963</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>604</v>
+        <v>541</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6011</v>
+        <v>241</v>
       </c>
       <c r="C2" t="n">
-        <v>5718</v>
+        <v>12010</v>
       </c>
       <c r="D2" t="n">
-        <v>16883</v>
+        <v>13665</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2808</v>
+        <v>301</v>
       </c>
       <c r="C3" t="n">
-        <v>2097</v>
+        <v>6398</v>
       </c>
       <c r="D3" t="n">
-        <v>11592</v>
+        <v>6752</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3002</v>
+        <v>476</v>
       </c>
       <c r="C4" t="n">
-        <v>3473</v>
+        <v>4802</v>
       </c>
       <c r="D4" t="n">
-        <v>11407</v>
+        <v>6643</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2864</v>
+        <v>632</v>
       </c>
       <c r="C5" t="n">
-        <v>5693</v>
+        <v>6827</v>
       </c>
       <c r="D5" t="n">
-        <v>6723</v>
+        <v>4343</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1898</v>
+        <v>503</v>
       </c>
       <c r="C6" t="n">
-        <v>6737</v>
+        <v>7947</v>
       </c>
       <c r="D6" t="n">
-        <v>2610</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>683</v>
+        <v>219</v>
       </c>
       <c r="C7" t="n">
-        <v>5082</v>
+        <v>6601</v>
       </c>
       <c r="D7" t="n">
-        <v>923</v>
+        <v>826</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>138</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>2708</v>
+        <v>3415</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1027</v>
+        <v>1126</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7860</v>
+        <v>4757</v>
       </c>
       <c r="C2" t="n">
-        <v>4818</v>
+        <v>12764</v>
       </c>
       <c r="D2" t="n">
-        <v>7890</v>
+        <v>8297</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4252</v>
+        <v>638</v>
       </c>
       <c r="C2" t="n">
-        <v>3202</v>
+        <v>8547</v>
       </c>
       <c r="D2" t="n">
-        <v>12425</v>
+        <v>13707</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3890</v>
+        <v>232</v>
       </c>
       <c r="C3" t="n">
-        <v>3143</v>
+        <v>7736</v>
       </c>
       <c r="D3" t="n">
-        <v>12975</v>
+        <v>7258</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4177</v>
+        <v>357</v>
       </c>
       <c r="C4" t="n">
-        <v>5269</v>
+        <v>5406</v>
       </c>
       <c r="D4" t="n">
-        <v>11733</v>
+        <v>6392</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1859</v>
+        <v>525</v>
       </c>
       <c r="C5" t="n">
-        <v>8986</v>
+        <v>5764</v>
       </c>
       <c r="D5" t="n">
-        <v>6184</v>
+        <v>4542</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>631</v>
+        <v>511</v>
       </c>
       <c r="C6" t="n">
-        <v>6366</v>
+        <v>7413</v>
       </c>
       <c r="D6" t="n">
-        <v>2056</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>127</v>
+        <v>295</v>
       </c>
       <c r="C7" t="n">
-        <v>2653</v>
+        <v>7139</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>988</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>1006</v>
+        <v>4597</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>1977</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>161</v>
+        <v>603</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7349</v>
+        <v>4943</v>
       </c>
       <c r="C2" t="n">
-        <v>4368</v>
+        <v>12067</v>
       </c>
       <c r="D2" t="n">
-        <v>21225</v>
+        <v>12668</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3338</v>
+        <v>1572</v>
       </c>
       <c r="C3" t="n">
-        <v>2428</v>
+        <v>5040</v>
       </c>
       <c r="D3" t="n">
-        <v>1964</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5463</v>
+        <v>3245</v>
       </c>
       <c r="C2" t="n">
-        <v>5200</v>
+        <v>7078</v>
       </c>
       <c r="D2" t="n">
-        <v>16266</v>
+        <v>12057</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4391</v>
+        <v>2751</v>
       </c>
       <c r="C3" t="n">
-        <v>3040</v>
+        <v>7968</v>
       </c>
       <c r="D3" t="n">
-        <v>5055</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1484</v>
+        <v>752</v>
       </c>
       <c r="C4" t="n">
+        <v>3192</v>
+      </c>
+      <c r="D4" t="n">
         <v>1466</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1577</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>343</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5142</v>
+        <v>3388</v>
       </c>
       <c r="C2" t="n">
-        <v>5602</v>
+        <v>5894</v>
       </c>
       <c r="D2" t="n">
-        <v>19007</v>
+        <v>18570</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4049</v>
+        <v>2474</v>
       </c>
       <c r="C3" t="n">
-        <v>3650</v>
+        <v>6417</v>
       </c>
       <c r="D3" t="n">
-        <v>6484</v>
+        <v>4711</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2490</v>
+        <v>1539</v>
       </c>
       <c r="C4" t="n">
-        <v>2327</v>
+        <v>5968</v>
       </c>
       <c r="D4" t="n">
-        <v>2196</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>668</v>
+        <v>368</v>
       </c>
       <c r="C5" t="n">
-        <v>894</v>
+        <v>1921</v>
       </c>
       <c r="D5" t="n">
-        <v>1209</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5864</v>
+        <v>2322</v>
       </c>
       <c r="C2" t="n">
-        <v>5901</v>
+        <v>6232</v>
       </c>
       <c r="D2" t="n">
-        <v>24389</v>
+        <v>20656</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3761</v>
+        <v>2403</v>
       </c>
       <c r="C3" t="n">
-        <v>4051</v>
+        <v>5307</v>
       </c>
       <c r="D3" t="n">
-        <v>7931</v>
+        <v>6589</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2766</v>
+        <v>1727</v>
       </c>
       <c r="C4" t="n">
-        <v>2967</v>
+        <v>6098</v>
       </c>
       <c r="D4" t="n">
-        <v>2890</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1321</v>
+        <v>799</v>
       </c>
       <c r="C5" t="n">
-        <v>1632</v>
+        <v>4095</v>
       </c>
       <c r="D5" t="n">
-        <v>1352</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>348</v>
+        <v>213</v>
       </c>
       <c r="C6" t="n">
-        <v>600</v>
+        <v>1134</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>836</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8032</v>
+        <v>2800</v>
       </c>
       <c r="C2" t="n">
-        <v>5588</v>
+        <v>10584</v>
       </c>
       <c r="D2" t="n">
-        <v>23442</v>
+        <v>23078</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3496</v>
+        <v>1960</v>
       </c>
       <c r="C3" t="n">
-        <v>4105</v>
+        <v>5084</v>
       </c>
       <c r="D3" t="n">
-        <v>9289</v>
+        <v>8263</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2040</v>
+        <v>1751</v>
       </c>
       <c r="C4" t="n">
-        <v>2932</v>
+        <v>5494</v>
       </c>
       <c r="D4" t="n">
-        <v>3222</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1069</v>
+        <v>1082</v>
       </c>
       <c r="C5" t="n">
-        <v>1709</v>
+        <v>5048</v>
       </c>
       <c r="D5" t="n">
-        <v>1290</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>398</v>
+        <v>431</v>
       </c>
       <c r="C6" t="n">
-        <v>750</v>
+        <v>2599</v>
       </c>
       <c r="D6" t="n">
-        <v>767</v>
+        <v>883</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="C7" t="n">
-        <v>304</v>
+        <v>706</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5829</v>
+        <v>1867</v>
       </c>
       <c r="C2" t="n">
-        <v>5589</v>
+        <v>15808</v>
       </c>
       <c r="D2" t="n">
-        <v>29628</v>
+        <v>19550</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4839</v>
+        <v>1915</v>
       </c>
       <c r="C3" t="n">
-        <v>4279</v>
+        <v>6745</v>
       </c>
       <c r="D3" t="n">
-        <v>11081</v>
+        <v>9827</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2442</v>
+        <v>1583</v>
       </c>
       <c r="C4" t="n">
-        <v>3591</v>
+        <v>5175</v>
       </c>
       <c r="D4" t="n">
-        <v>4405</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1397</v>
+        <v>1226</v>
       </c>
       <c r="C5" t="n">
-        <v>2384</v>
+        <v>5157</v>
       </c>
       <c r="D5" t="n">
-        <v>1640</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>681</v>
+        <v>642</v>
       </c>
       <c r="C6" t="n">
-        <v>1302</v>
+        <v>3676</v>
       </c>
       <c r="D6" t="n">
-        <v>849</v>
+        <v>931</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C7" t="n">
-        <v>561</v>
+        <v>1577</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>267</v>
+        <v>480</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>154</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5170</v>
+        <v>1819</v>
       </c>
       <c r="C2" t="n">
-        <v>6990</v>
+        <v>9864</v>
       </c>
       <c r="D2" t="n">
-        <v>25691</v>
+        <v>15515</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4393</v>
+        <v>2653</v>
       </c>
       <c r="C3" t="n">
-        <v>4325</v>
+        <v>11045</v>
       </c>
       <c r="D3" t="n">
-        <v>13250</v>
+        <v>10629</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3143</v>
+        <v>1132</v>
       </c>
       <c r="C4" t="n">
-        <v>3912</v>
+        <v>8130</v>
       </c>
       <c r="D4" t="n">
-        <v>5510</v>
+        <v>3677</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1682</v>
+        <v>593</v>
       </c>
       <c r="C5" t="n">
-        <v>3006</v>
+        <v>3602</v>
       </c>
       <c r="D5" t="n">
-        <v>2121</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>952</v>
+        <v>218</v>
       </c>
       <c r="C6" t="n">
-        <v>1855</v>
+        <v>1545</v>
       </c>
       <c r="D6" t="n">
-        <v>981</v>
+        <v>640</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>403</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>960</v>
+        <v>470</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>419</v>
+        <v>276</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
